--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53946,7 +53946,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -54215,7 +54215,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>90265</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -54480,7 +54480,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>77031</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -54810,7 +54810,7 @@
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -55079,7 +55079,7 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -55348,7 +55348,7 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -55617,7 +55617,7 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>30004</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -55882,7 +55882,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>85120</t>
+          <t>84531</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53931,7 +53931,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>09/05/1970</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53976,7 +53976,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>05/11/2019</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54004,12 +54004,12 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$20.14</t>
+          <t>$19.33</t>
         </is>
       </c>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>$30.21</t>
+          <t>$28.99</t>
         </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
@@ -54045,12 +54045,12 @@
       <c r="AA18" s="11" t="n"/>
       <c r="AB18" s="11" t="inlineStr">
         <is>
-          <t>$19.57</t>
+          <t>$18.80</t>
         </is>
       </c>
       <c r="AC18" s="11" t="inlineStr">
         <is>
-          <t>$29.36</t>
+          <t>$28.20</t>
         </is>
       </c>
       <c r="AD18" s="11" t="inlineStr">
@@ -54070,18 +54070,18 @@
       </c>
       <c r="AG18" s="11" t="inlineStr">
         <is>
-          <t>$42,300.00</t>
+          <t>$40,700.00</t>
         </is>
       </c>
       <c r="AH18" s="11" t="n"/>
       <c r="AI18" s="11" t="inlineStr">
         <is>
-          <t>$18.99</t>
+          <t>$18.22</t>
         </is>
       </c>
       <c r="AJ18" s="11" t="inlineStr">
         <is>
-          <t>$28.48</t>
+          <t>$27.33</t>
         </is>
       </c>
       <c r="AK18" s="11" t="inlineStr">
@@ -54101,18 +54101,18 @@
       </c>
       <c r="AN18" s="11" t="inlineStr">
         <is>
-          <t>$41,100.00</t>
+          <t>$39,500.00</t>
         </is>
       </c>
       <c r="AO18" s="11" t="n"/>
       <c r="AP18" s="11" t="inlineStr">
         <is>
-          <t>$18.41</t>
+          <t>$17.69</t>
         </is>
       </c>
       <c r="AQ18" s="11" t="inlineStr">
         <is>
-          <t>$27.62</t>
+          <t>$26.54</t>
         </is>
       </c>
       <c r="AR18" s="11" t="inlineStr">
@@ -54132,7 +54132,7 @@
       </c>
       <c r="AU18" s="11" t="inlineStr">
         <is>
-          <t>$39,800.00</t>
+          <t>$38,300.00</t>
         </is>
       </c>
       <c r="AV18" s="11" t="inlineStr">
@@ -54200,7 +54200,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>09/13/1986</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54245,7 +54245,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>10/23/2013</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54273,12 +54273,12 @@
       <c r="R19" s="14" t="n"/>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$15.38</t>
+          <t>$14.76</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr">
         <is>
-          <t>$23.07</t>
+          <t>$22.14</t>
         </is>
       </c>
       <c r="U19" s="11" t="inlineStr">
@@ -54314,12 +54314,12 @@
       <c r="AA19" s="11" t="n"/>
       <c r="AB19" s="11" t="inlineStr">
         <is>
-          <t>$14.95</t>
+          <t>$14.38</t>
         </is>
       </c>
       <c r="AC19" s="11" t="inlineStr">
         <is>
-          <t>$22.42</t>
+          <t>$21.57</t>
         </is>
       </c>
       <c r="AD19" s="11" t="inlineStr">
@@ -54339,18 +54339,18 @@
       </c>
       <c r="AG19" s="11" t="inlineStr">
         <is>
-          <t>$32,300.00</t>
+          <t>$31,100.00</t>
         </is>
       </c>
       <c r="AH19" s="11" t="n"/>
       <c r="AI19" s="11" t="inlineStr">
         <is>
-          <t>$14.52</t>
+          <t>$13.94</t>
         </is>
       </c>
       <c r="AJ19" s="11" t="inlineStr">
         <is>
-          <t>$21.78</t>
+          <t>$20.91</t>
         </is>
       </c>
       <c r="AK19" s="11" t="inlineStr">
@@ -54370,18 +54370,18 @@
       </c>
       <c r="AN19" s="11" t="inlineStr">
         <is>
-          <t>$31,400.00</t>
+          <t>$30,200.00</t>
         </is>
       </c>
       <c r="AO19" s="11" t="n"/>
       <c r="AP19" s="11" t="inlineStr">
         <is>
-          <t>$14.09</t>
+          <t>$13.51</t>
         </is>
       </c>
       <c r="AQ19" s="11" t="inlineStr">
         <is>
-          <t>$21.13</t>
+          <t>$20.27</t>
         </is>
       </c>
       <c r="AR19" s="11" t="inlineStr">
@@ -54401,7 +54401,7 @@
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>$30,500.00</t>
+          <t>$29,300.00</t>
         </is>
       </c>
       <c r="AV19" s="11" t="inlineStr">
@@ -54465,7 +54465,7 @@
       <c r="A20" s="23" t="inlineStr"/>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>01/01/1962</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -54510,7 +54510,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54538,12 +54538,12 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$16.44</t>
+          <t>$15.77</t>
         </is>
       </c>
       <c r="T20" s="13" t="inlineStr">
         <is>
-          <t>$24.66</t>
+          <t>$23.66</t>
         </is>
       </c>
       <c r="U20" s="11" t="inlineStr">
@@ -54579,12 +54579,12 @@
       <c r="AA20" s="11" t="n"/>
       <c r="AB20" s="11" t="inlineStr">
         <is>
-          <t>$15.96</t>
+          <t>$15.34</t>
         </is>
       </c>
       <c r="AC20" s="11" t="inlineStr">
         <is>
-          <t>$23.94</t>
+          <t>$23.01</t>
         </is>
       </c>
       <c r="AD20" s="11" t="inlineStr">
@@ -54604,18 +54604,18 @@
       </c>
       <c r="AG20" s="11" t="inlineStr">
         <is>
-          <t>$34,500.00</t>
+          <t>$33,200.00</t>
         </is>
       </c>
       <c r="AH20" s="11" t="n"/>
       <c r="AI20" s="11" t="inlineStr">
         <is>
-          <t>$15.48</t>
+          <t>$14.86</t>
         </is>
       </c>
       <c r="AJ20" s="11" t="inlineStr">
         <is>
-          <t>$23.22</t>
+          <t>$22.29</t>
         </is>
       </c>
       <c r="AK20" s="11" t="inlineStr">
@@ -54635,18 +54635,18 @@
       </c>
       <c r="AN20" s="11" t="inlineStr">
         <is>
-          <t>$33,500.00</t>
+          <t>$32,200.00</t>
         </is>
       </c>
       <c r="AO20" s="11" t="n"/>
       <c r="AP20" s="11" t="inlineStr">
         <is>
-          <t>$15.05</t>
+          <t>$14.42</t>
         </is>
       </c>
       <c r="AQ20" s="11" t="inlineStr">
         <is>
-          <t>$22.58</t>
+          <t>$21.63</t>
         </is>
       </c>
       <c r="AR20" s="11" t="inlineStr">
@@ -54666,7 +54666,7 @@
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>$32,600.00</t>
+          <t>$31,300.00</t>
         </is>
       </c>
       <c r="AV20" s="11" t="inlineStr">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>07/11/1984</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -54840,7 +54840,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>10/23/2019</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -54868,12 +54868,12 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$11.44</t>
+          <t>$10.96</t>
         </is>
       </c>
       <c r="T22" s="13" t="inlineStr">
         <is>
-          <t>$17.16</t>
+          <t>$16.44</t>
         </is>
       </c>
       <c r="U22" s="11" t="inlineStr">
@@ -54909,12 +54909,12 @@
       <c r="AA22" s="11" t="n"/>
       <c r="AB22" s="11" t="inlineStr">
         <is>
-          <t>$11.11</t>
+          <t>$10.67</t>
         </is>
       </c>
       <c r="AC22" s="11" t="inlineStr">
         <is>
-          <t>$16.66</t>
+          <t>$16.00</t>
         </is>
       </c>
       <c r="AD22" s="11" t="inlineStr">
@@ -54934,18 +54934,18 @@
       </c>
       <c r="AG22" s="11" t="inlineStr">
         <is>
-          <t>$24,000.00</t>
+          <t>$23,100.00</t>
         </is>
       </c>
       <c r="AH22" s="11" t="n"/>
       <c r="AI22" s="11" t="inlineStr">
         <is>
-          <t>$10.77</t>
+          <t>$10.34</t>
         </is>
       </c>
       <c r="AJ22" s="11" t="inlineStr">
         <is>
-          <t>$16.16</t>
+          <t>$15.51</t>
         </is>
       </c>
       <c r="AK22" s="11" t="inlineStr">
@@ -54965,18 +54965,18 @@
       </c>
       <c r="AN22" s="11" t="inlineStr">
         <is>
-          <t>$23,300.00</t>
+          <t>$22,400.00</t>
         </is>
       </c>
       <c r="AO22" s="11" t="n"/>
       <c r="AP22" s="11" t="inlineStr">
         <is>
-          <t>$10.43</t>
+          <t>$10.00</t>
         </is>
       </c>
       <c r="AQ22" s="11" t="inlineStr">
         <is>
-          <t>$15.64</t>
+          <t>$15.00</t>
         </is>
       </c>
       <c r="AR22" s="11" t="inlineStr">
@@ -54996,7 +54996,7 @@
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>$22,600.00</t>
+          <t>$21,700.00</t>
         </is>
       </c>
       <c r="AV22" s="11" t="inlineStr">
@@ -55064,7 +55064,7 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>07/11/1984</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -55109,7 +55109,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>10/23/2019</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55137,12 +55137,12 @@
       <c r="R23" s="14" t="n"/>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$11.20</t>
+          <t>$10.77</t>
         </is>
       </c>
       <c r="T23" s="13" t="inlineStr">
         <is>
-          <t>$16.80</t>
+          <t>$16.16</t>
         </is>
       </c>
       <c r="U23" s="11" t="inlineStr">
@@ -55178,12 +55178,12 @@
       <c r="AA23" s="11" t="n"/>
       <c r="AB23" s="11" t="inlineStr">
         <is>
-          <t>$10.87</t>
+          <t>$10.43</t>
         </is>
       </c>
       <c r="AC23" s="11" t="inlineStr">
         <is>
-          <t>$16.30</t>
+          <t>$15.64</t>
         </is>
       </c>
       <c r="AD23" s="11" t="inlineStr">
@@ -55203,18 +55203,18 @@
       </c>
       <c r="AG23" s="11" t="inlineStr">
         <is>
-          <t>$23,500.00</t>
+          <t>$22,600.00</t>
         </is>
       </c>
       <c r="AH23" s="11" t="n"/>
       <c r="AI23" s="11" t="inlineStr">
         <is>
-          <t>$10.53</t>
+          <t>$10.10</t>
         </is>
       </c>
       <c r="AJ23" s="11" t="inlineStr">
         <is>
-          <t>$15.79</t>
+          <t>$15.15</t>
         </is>
       </c>
       <c r="AK23" s="11" t="inlineStr">
@@ -55234,18 +55234,18 @@
       </c>
       <c r="AN23" s="11" t="inlineStr">
         <is>
-          <t>$22,800.00</t>
+          <t>$21,900.00</t>
         </is>
       </c>
       <c r="AO23" s="11" t="n"/>
       <c r="AP23" s="11" t="inlineStr">
         <is>
-          <t>$10.24</t>
+          <t>$9.81</t>
         </is>
       </c>
       <c r="AQ23" s="11" t="inlineStr">
         <is>
-          <t>$15.36</t>
+          <t>$14.71</t>
         </is>
       </c>
       <c r="AR23" s="11" t="inlineStr">
@@ -55265,7 +55265,7 @@
       </c>
       <c r="AU23" s="11" t="inlineStr">
         <is>
-          <t>$22,200.00</t>
+          <t>$21,300.00</t>
         </is>
       </c>
       <c r="AV23" s="11" t="inlineStr">
@@ -55333,12 +55333,12 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>02/10/1975</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -55378,7 +55378,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>06/13/2015</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55406,12 +55406,12 @@
       <c r="R24" s="14" t="n"/>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$19.52</t>
+          <t>$18.75</t>
         </is>
       </c>
       <c r="T24" s="13" t="inlineStr">
         <is>
-          <t>$29.28</t>
+          <t>$28.12</t>
         </is>
       </c>
       <c r="U24" s="11" t="inlineStr">
@@ -55447,12 +55447,12 @@
       <c r="AA24" s="11" t="n"/>
       <c r="AB24" s="11" t="inlineStr">
         <is>
-          <t>$18.94</t>
+          <t>$18.17</t>
         </is>
       </c>
       <c r="AC24" s="11" t="inlineStr">
         <is>
-          <t>$28.41</t>
+          <t>$27.26</t>
         </is>
       </c>
       <c r="AD24" s="11" t="inlineStr">
@@ -55472,18 +55472,18 @@
       </c>
       <c r="AG24" s="11" t="inlineStr">
         <is>
-          <t>$41,000.00</t>
+          <t>$39,400.00</t>
         </is>
       </c>
       <c r="AH24" s="11" t="n"/>
       <c r="AI24" s="11" t="inlineStr">
         <is>
-          <t>$18.41</t>
+          <t>$17.69</t>
         </is>
       </c>
       <c r="AJ24" s="11" t="inlineStr">
         <is>
-          <t>$27.62</t>
+          <t>$26.54</t>
         </is>
       </c>
       <c r="AK24" s="11" t="inlineStr">
@@ -55503,18 +55503,18 @@
       </c>
       <c r="AN24" s="11" t="inlineStr">
         <is>
-          <t>$39,800.00</t>
+          <t>$38,300.00</t>
         </is>
       </c>
       <c r="AO24" s="11" t="n"/>
       <c r="AP24" s="11" t="inlineStr">
         <is>
-          <t>$17.88</t>
+          <t>$17.16</t>
         </is>
       </c>
       <c r="AQ24" s="11" t="inlineStr">
         <is>
-          <t>$26.82</t>
+          <t>$25.74</t>
         </is>
       </c>
       <c r="AR24" s="11" t="inlineStr">
@@ -55534,7 +55534,7 @@
       </c>
       <c r="AU24" s="11" t="inlineStr">
         <is>
-          <t>$38,700.00</t>
+          <t>$37,200.00</t>
         </is>
       </c>
       <c r="AV24" s="11" t="inlineStr">
@@ -55602,12 +55602,12 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>02/18/1999</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -55647,7 +55647,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>11/25/2019</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55675,12 +55675,12 @@
       <c r="R25" s="14" t="n"/>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$16.01</t>
+          <t>$15.38</t>
         </is>
       </c>
       <c r="T25" s="13" t="inlineStr">
         <is>
-          <t>$24.02</t>
+          <t>$23.07</t>
         </is>
       </c>
       <c r="U25" s="11" t="inlineStr">
@@ -55716,12 +55716,12 @@
       <c r="AA25" s="11" t="n"/>
       <c r="AB25" s="11" t="inlineStr">
         <is>
-          <t>$15.53</t>
+          <t>$14.90</t>
         </is>
       </c>
       <c r="AC25" s="11" t="inlineStr">
         <is>
-          <t>$23.29</t>
+          <t>$22.35</t>
         </is>
       </c>
       <c r="AD25" s="11" t="inlineStr">
@@ -55741,18 +55741,18 @@
       </c>
       <c r="AG25" s="11" t="inlineStr">
         <is>
-          <t>$33,600.00</t>
+          <t>$32,300.00</t>
         </is>
       </c>
       <c r="AH25" s="11" t="n"/>
       <c r="AI25" s="11" t="inlineStr">
         <is>
-          <t>$15.10</t>
+          <t>$14.47</t>
         </is>
       </c>
       <c r="AJ25" s="11" t="inlineStr">
         <is>
-          <t>$22.65</t>
+          <t>$21.71</t>
         </is>
       </c>
       <c r="AK25" s="11" t="inlineStr">
@@ -55772,18 +55772,18 @@
       </c>
       <c r="AN25" s="11" t="inlineStr">
         <is>
-          <t>$32,700.00</t>
+          <t>$31,400.00</t>
         </is>
       </c>
       <c r="AO25" s="11" t="n"/>
       <c r="AP25" s="11" t="inlineStr">
         <is>
-          <t>$14.66</t>
+          <t>$14.09</t>
         </is>
       </c>
       <c r="AQ25" s="11" t="inlineStr">
         <is>
-          <t>$21.99</t>
+          <t>$21.13</t>
         </is>
       </c>
       <c r="AR25" s="11" t="inlineStr">
@@ -55803,7 +55803,7 @@
       </c>
       <c r="AU25" s="11" t="inlineStr">
         <is>
-          <t>$31,700.00</t>
+          <t>$30,500.00</t>
         </is>
       </c>
       <c r="AV25" s="11" t="inlineStr">
@@ -55867,7 +55867,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>05/10/1990</t>
+          <t>01/25/1986</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -55912,7 +55912,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>03/02/2020</t>
+          <t>04/09/2021</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -55936,12 +55936,12 @@
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$11.54</t>
+          <t>$11.06</t>
         </is>
       </c>
       <c r="T26" s="13" t="inlineStr">
         <is>
-          <t>$17.31</t>
+          <t>$16.59</t>
         </is>
       </c>
       <c r="U26" s="11" t="inlineStr">
@@ -55977,12 +55977,12 @@
       <c r="AA26" s="11" t="n"/>
       <c r="AB26" s="11" t="inlineStr">
         <is>
-          <t>$11.20</t>
+          <t>$10.77</t>
         </is>
       </c>
       <c r="AC26" s="11" t="inlineStr">
         <is>
-          <t>$16.80</t>
+          <t>$16.16</t>
         </is>
       </c>
       <c r="AD26" s="11" t="inlineStr">
@@ -56002,18 +56002,18 @@
       </c>
       <c r="AG26" s="11" t="inlineStr">
         <is>
-          <t>$24,200.00</t>
+          <t>$23,300.00</t>
         </is>
       </c>
       <c r="AH26" s="11" t="n"/>
       <c r="AI26" s="11" t="inlineStr">
         <is>
-          <t>$10.87</t>
+          <t>$10.43</t>
         </is>
       </c>
       <c r="AJ26" s="11" t="inlineStr">
         <is>
-          <t>$16.30</t>
+          <t>$15.64</t>
         </is>
       </c>
       <c r="AK26" s="11" t="inlineStr">
@@ -56033,18 +56033,18 @@
       </c>
       <c r="AN26" s="11" t="inlineStr">
         <is>
-          <t>$23,500.00</t>
+          <t>$22,600.00</t>
         </is>
       </c>
       <c r="AO26" s="11" t="n"/>
       <c r="AP26" s="11" t="inlineStr">
         <is>
-          <t>$10.53</t>
+          <t>$10.10</t>
         </is>
       </c>
       <c r="AQ26" s="11" t="inlineStr">
         <is>
-          <t>$15.79</t>
+          <t>$15.15</t>
         </is>
       </c>
       <c r="AR26" s="11" t="inlineStr">
@@ -56064,7 +56064,7 @@
       </c>
       <c r="AU26" s="11" t="inlineStr">
         <is>
-          <t>$22,800.00</t>
+          <t>$21,900.00</t>
         </is>
       </c>
       <c r="AV26" s="11" t="inlineStr">

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -8,9 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Census Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Census Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENANCE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
@@ -33,6 +33,7 @@
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
     <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="_____dc1" hidden="1">{#N/A,#N/A,FALSE,"COVER PAGE";#N/A,#N/A,FALSE,"HIGHLITES";#N/A,#N/A,FALSE,"INC STATE (1)";#N/A,#N/A,FALSE,"DPC BY DEPT";#N/A,#N/A,FALSE,"FIXED COSTS";#N/A,#N/A,FALSE,"PRODUCTION";#N/A,#N/A,FALSE,"SALES TRND";#N/A,#N/A,FALSE,"BALANCE SHEET";#N/A,#N/A,FALSE,"INVENTORY";#N/A,#N/A,FALSE,"MFG VAR";#N/A,#N/A,FALSE,"OVRHD SPND";#N/A,#N/A,FALSE,"ENERGY COSTS";#N/A,#N/A,FALSE,"MAINTENANCE";#N/A,#N/A,FALSE,"LABOR";#N/A,#N/A,FALSE,"ACTVSFORECAST"}</definedName>
@@ -53976,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>05/11/2019</t>
+          <t>05/11/2023</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54200,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>09/13/1986</t>
+          <t>08/24/1973</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54245,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>10/23/2013</t>
+          <t>12/27/2017</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54795,12 +54796,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>07/11/1984</t>
+          <t>06/06/1963</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -54840,7 +54841,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>10/23/2019</t>
+          <t>01/02/2018</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55064,12 +55065,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>07/11/1984</t>
+          <t>06/06/1963</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -55109,7 +55110,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>10/23/2019</t>
+          <t>01/02/2018</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55333,7 +55334,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>02/10/1975</t>
+          <t>10/26/1987</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -55378,7 +55379,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>06/13/2015</t>
+          <t>12/28/2016</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55602,12 +55603,12 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>02/18/1999</t>
+          <t>07/07/1964</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -55647,7 +55648,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>11/25/2019</t>
+          <t>01/03/2023</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55867,12 +55868,12 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>01/25/1986</t>
+          <t>10/26/1999</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -55912,7 +55913,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>04/09/2021</t>
+          <t>12/28/2019</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -63325,4 +63326,471 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nine Dean — simulated census: data provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>warehouse table</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ext_mit_expense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>301,824</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Engine A basket components</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MIT · Living Wage Calculator</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ext_mit_living_wage</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>113,184</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mit:livingwage.mit.edu:2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Engine A living-wage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ext_epi_cost</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>502,880</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Engine A basket (food, childcare, medical, housing, other)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EPI · Family Budget Calculator</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ext_epi_county</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,143</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>epi:2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Engine A county coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACS · B25064 median gross rent</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ext_acs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>acs:5y2023-B25064</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Engine A housing candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CNT · H+T Affordability Index</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ext_cnt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3,144</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cnt:2022</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Engine A transportation (override, not MAX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BLS OEWS · state wages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ext_bls_oews_state_wage</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>35,427</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>May2024</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wages by state+SOC (p10/p25/median); prevailing-wage overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>O*NET · SOC occupations</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_occupation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1,016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>job titles and SOC codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>O*NET · SOC alternate titles</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ext_onet_soc_alt_title</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>55,119</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O*NET 29.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>title → SOC matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Census · ZCTA↔county crosswalk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ext_census_zcta_county</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>23,355</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>census_zcta:2020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>residence ZIP → county</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Census · county gazetteer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ext_census_county</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,222</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>census_county:2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>county names / states</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A Better Balance · PSL statutes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ext_abb_psl_law</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>abb:2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Engine B floors (cap / preempted / no-cap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KFF · EHBS benchmarks</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ext_kff_ehbs_health_benchmarks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>kff_ehbs:2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Engine C employer-contribution thresholds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Peterson-KFF · OOP cost-sharing</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ext_peterson_kff_oop_costsharing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>live scrape; page modified 2026-02-11</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Engine C out-of-pocket exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PolicyEngine US</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>in-process library (not a warehouse table)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>policyengine-us 1.745.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Engine A federal + state + payroll + local tax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53932,12 +53932,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>09/05/1970</t>
+          <t>02/14/1967</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>05/11/2023</t>
+          <t>07/07/2024</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>08/24/1973</t>
+          <t>03/03/1972</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>12/27/2017</t>
+          <t>10/13/2012</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54511,7 +54511,7 @@
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>05/07/2012</t>
         </is>
       </c>
       <c r="L20" s="14" t="n"/>
@@ -54796,12 +54796,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>06/06/1963</t>
+          <t>03/15/2000</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -54841,7 +54841,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>01/02/2018</t>
+          <t>12/28/2019</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55065,12 +55065,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>06/06/1963</t>
+          <t>03/15/2000</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -55110,7 +55110,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>01/02/2018</t>
+          <t>12/28/2019</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55334,7 +55334,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>10/26/1987</t>
+          <t>08/08/1977</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>12/28/2016</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55603,12 +55603,12 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>07/07/1964</t>
+          <t>04/12/1989</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -55648,7 +55648,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>01/03/2023</t>
+          <t>10/18/2020</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55868,12 +55868,12 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>10/26/1999</t>
+          <t>05/09/1990</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>12/28/2019</t>
+          <t>12/02/2025</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -63354,7 +63354,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:01 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53932,7 +53932,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>02/14/1967</t>
+          <t>06/10/1963</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53977,7 +53977,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>07/07/2024</t>
+          <t>04/25/2014</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,12 +54201,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>03/03/1972</t>
+          <t>04/16/1965</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -54246,7 +54246,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>10/13/2012</t>
+          <t>10/22/2024</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>03/15/2000</t>
+          <t>05/25/1986</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -54841,7 +54841,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>12/28/2019</t>
+          <t>01/18/2024</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55065,7 +55065,7 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>03/15/2000</t>
+          <t>05/25/1986</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -55110,7 +55110,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>12/28/2019</t>
+          <t>01/18/2024</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55334,7 +55334,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>08/08/1977</t>
+          <t>12/04/2001</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>09/13/2023</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55603,7 +55603,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>04/12/1989</t>
+          <t>04/28/1997</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -55648,7 +55648,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>10/18/2020</t>
+          <t>11/08/2018</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55868,7 +55868,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>05/09/1990</t>
+          <t>09/09/1994</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -55913,7 +55913,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>02/15/2020</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -63354,7 +63354,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 00:25 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53075,7 +53075,11 @@
           <t>Company Name:</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n"/>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>Halstead Logistics Group, LLC</t>
+        </is>
+      </c>
       <c r="C8" s="46" t="n"/>
       <c r="D8" s="46" t="n"/>
       <c r="E8" s="45" t="n"/>
@@ -53140,7 +53144,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B9" s="43" t="n"/>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
       <c r="C9" s="43" t="n"/>
       <c r="D9" s="43" t="n"/>
       <c r="E9" s="43" t="n"/>
@@ -53932,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>06/10/1963</t>
+          <t>07/23/1980</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53977,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>04/25/2014</t>
+          <t>04/03/2019</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54201,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>04/16/1965</t>
+          <t>08/08/1993</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54246,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>10/22/2024</t>
+          <t>01/21/2021</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54796,12 +54804,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>05/25/1986</t>
+          <t>08/04/1985</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -54841,7 +54849,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>01/18/2024</t>
+          <t>01/13/2025</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55065,12 +55073,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>05/25/1986</t>
+          <t>08/04/1985</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -55110,7 +55118,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>01/18/2024</t>
+          <t>01/13/2025</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55334,12 +55342,12 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>12/04/2001</t>
+          <t>11/11/1964</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -55379,7 +55387,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>09/13/2023</t>
+          <t>07/01/2021</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55603,7 +55611,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>04/28/1997</t>
+          <t>12/20/1997</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -55648,7 +55656,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>11/08/2018</t>
+          <t>10/01/2024</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55868,12 +55876,12 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>09/09/1994</t>
+          <t>08/24/1989</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -55913,7 +55921,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>02/15/2020</t>
+          <t>08/15/2024</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -63354,7 +63362,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 12:56 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53940,7 +53940,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>07/23/1980</t>
+          <t>03/19/1972</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>04/03/2019</t>
+          <t>08/13/2020</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>08/08/1993</t>
+          <t>02/14/1995</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>01/21/2021</t>
+          <t>07/23/2025</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54804,7 +54804,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>08/04/1985</t>
+          <t>04/24/2001</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>12/09/2023</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55073,7 +55073,7 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>08/04/1985</t>
+          <t>04/24/2001</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -55118,7 +55118,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>12/09/2023</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>11/11/1964</t>
+          <t>11/03/1976</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -55387,7 +55387,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>07/01/2021</t>
+          <t>11/12/2017</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55611,7 +55611,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>12/20/1997</t>
+          <t>02/14/1979</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -55656,7 +55656,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>10/01/2024</t>
+          <t>07/24/2024</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55876,7 +55876,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>08/24/1989</t>
+          <t>06/18/1987</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -55921,7 +55921,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>08/15/2024</t>
+          <t>03/02/2023</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -56134,65 +56134,269 @@
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="23" t="n"/>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="14" t="n"/>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="14" t="n"/>
-      <c r="K27" s="14" t="n"/>
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>ING-E28</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>11/23/1992</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>75751</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Sales Managers</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>TX Office</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>06/04/2021</t>
+        </is>
+      </c>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n"/>
-      <c r="N27" s="14" t="n"/>
-      <c r="O27" s="14" t="n"/>
-      <c r="P27" s="14" t="n"/>
-      <c r="Q27" s="14" t="n"/>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>Non-Exempt</t>
+        </is>
+      </c>
+      <c r="P27" s="14" t="inlineStr">
+        <is>
+          <t>Regular Full time (FT)</t>
+        </is>
+      </c>
+      <c r="Q27" s="14" t="inlineStr">
+        <is>
+          <t>Hourly</t>
+        </is>
+      </c>
       <c r="R27" s="14" t="n"/>
-      <c r="S27" s="14" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="11" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="11" t="n"/>
-      <c r="Z27" s="11" t="n"/>
+      <c r="S27" s="14" t="inlineStr">
+        <is>
+          <t>$22.60</t>
+        </is>
+      </c>
+      <c r="T27" s="13" t="inlineStr">
+        <is>
+          <t>$33.90</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>Annual performance</t>
+        </is>
+      </c>
+      <c r="X27" s="11" t="inlineStr">
+        <is>
+          <t>$2,000.00</t>
+        </is>
+      </c>
+      <c r="Y27" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="Z27" s="11" t="inlineStr">
+        <is>
+          <t>$49,000.00</t>
+        </is>
+      </c>
       <c r="AA27" s="11" t="n"/>
-      <c r="AB27" s="11" t="n"/>
-      <c r="AC27" s="11" t="n"/>
-      <c r="AD27" s="11" t="n"/>
-      <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="11" t="n"/>
-      <c r="AG27" s="11" t="n"/>
+      <c r="AB27" s="11" t="inlineStr">
+        <is>
+          <t>$21.97</t>
+        </is>
+      </c>
+      <c r="AC27" s="11" t="inlineStr">
+        <is>
+          <t>$32.95</t>
+        </is>
+      </c>
+      <c r="AD27" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AE27" s="11" t="inlineStr">
+        <is>
+          <t>$1,900.00</t>
+        </is>
+      </c>
+      <c r="AF27" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AG27" s="11" t="inlineStr">
+        <is>
+          <t>$47,600.00</t>
+        </is>
+      </c>
       <c r="AH27" s="11" t="n"/>
-      <c r="AI27" s="11" t="n"/>
-      <c r="AJ27" s="11" t="n"/>
-      <c r="AK27" s="11" t="n"/>
-      <c r="AL27" s="11" t="n"/>
-      <c r="AM27" s="11" t="n"/>
-      <c r="AN27" s="11" t="n"/>
+      <c r="AI27" s="11" t="inlineStr">
+        <is>
+          <t>$21.35</t>
+        </is>
+      </c>
+      <c r="AJ27" s="11" t="inlineStr">
+        <is>
+          <t>$32.03</t>
+        </is>
+      </c>
+      <c r="AK27" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AL27" s="11" t="inlineStr">
+        <is>
+          <t>$1,800.00</t>
+        </is>
+      </c>
+      <c r="AM27" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AN27" s="11" t="inlineStr">
+        <is>
+          <t>$46,200.00</t>
+        </is>
+      </c>
       <c r="AO27" s="11" t="n"/>
-      <c r="AP27" s="11" t="n"/>
-      <c r="AQ27" s="11" t="n"/>
-      <c r="AR27" s="11" t="n"/>
-      <c r="AS27" s="11" t="n"/>
-      <c r="AT27" s="11" t="n"/>
-      <c r="AU27" s="11" t="n"/>
-      <c r="AV27" s="11" t="n"/>
-      <c r="AW27" s="10" t="n"/>
-      <c r="AX27" s="10" t="n"/>
-      <c r="AY27" s="10" t="n"/>
-      <c r="AZ27" s="10" t="n"/>
-      <c r="BA27" s="10" t="n"/>
-      <c r="BB27" s="10" t="n"/>
-      <c r="BC27" s="10" t="n"/>
+      <c r="AP27" s="11" t="inlineStr">
+        <is>
+          <t>$20.72</t>
+        </is>
+      </c>
+      <c r="AQ27" s="11" t="inlineStr">
+        <is>
+          <t>$31.08</t>
+        </is>
+      </c>
+      <c r="AR27" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AS27" s="11" t="inlineStr">
+        <is>
+          <t>$1,800.00</t>
+        </is>
+      </c>
+      <c r="AT27" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AU27" s="11" t="inlineStr">
+        <is>
+          <t>$44,900.00</t>
+        </is>
+      </c>
+      <c r="AV27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AW27" s="10" t="inlineStr">
+        <is>
+          <t>EE / Employee Only</t>
+        </is>
+      </c>
+      <c r="AX27" s="10" t="inlineStr">
+        <is>
+          <t>Plan A $2000</t>
+        </is>
+      </c>
+      <c r="AY27" s="10" t="inlineStr">
+        <is>
+          <t>$800.00</t>
+        </is>
+      </c>
+      <c r="AZ27" s="10" t="inlineStr">
+        <is>
+          <t>$720.00</t>
+        </is>
+      </c>
+      <c r="BA27" s="10" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+      <c r="BB27" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC27" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
       <c r="BD27" s="20" t="n"/>
-      <c r="BE27" s="19" t="n"/>
-      <c r="BF27" s="19" t="n"/>
-      <c r="BG27" s="19" t="n"/>
+      <c r="BE27" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BF27" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BG27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="23" t="n"/>
@@ -63362,7 +63566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 18:20 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>07/21/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>03/19/1972</t>
+          <t>08/12/1997</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>08/13/2020</t>
+          <t>03/03/2017</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>02/14/1995</t>
+          <t>12/04/1985</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>07/23/2025</t>
+          <t>06/10/2012</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54804,12 +54804,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>04/24/2001</t>
+          <t>11/19/1984</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>12/09/2023</t>
+          <t>09/04/2017</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55073,12 +55073,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>04/24/2001</t>
+          <t>11/19/1984</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -55118,7 +55118,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>12/09/2023</t>
+          <t>09/04/2017</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55342,12 +55342,12 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>11/03/1976</t>
+          <t>12/04/1989</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -55387,7 +55387,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>11/12/2017</t>
+          <t>06/16/2017</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55611,7 +55611,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>02/14/1979</t>
+          <t>04/24/1997</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -55656,7 +55656,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>07/24/2024</t>
+          <t>03/17/2016</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55876,12 +55876,12 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>06/18/1987</t>
+          <t>11/23/1984</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -55921,7 +55921,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>03/02/2023</t>
+          <t>03/11/2014</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -56141,12 +56141,12 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>11/23/1992</t>
+          <t>04/04/1985</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -56182,7 +56182,7 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>08/10/2016</t>
         </is>
       </c>
       <c r="L27" s="14" t="n"/>
@@ -56399,248 +56399,1064 @@
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="23" t="n"/>
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>ING-E29</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>11/19/1968</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>75751</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>TX Office</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>06/11/2014</t>
+        </is>
+      </c>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
-      <c r="N28" s="14" t="n"/>
-      <c r="O28" s="14" t="n"/>
-      <c r="P28" s="14" t="n"/>
-      <c r="Q28" s="14" t="n"/>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>Non-Exempt</t>
+        </is>
+      </c>
+      <c r="P28" s="14" t="inlineStr">
+        <is>
+          <t>Regular Full time (FT)</t>
+        </is>
+      </c>
+      <c r="Q28" s="14" t="inlineStr">
+        <is>
+          <t>Hourly</t>
+        </is>
+      </c>
       <c r="R28" s="14" t="n"/>
-      <c r="S28" s="14" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="11" t="n"/>
-      <c r="V28" s="11" t="n"/>
-      <c r="W28" s="11" t="n"/>
-      <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="11" t="n"/>
-      <c r="Z28" s="11" t="n"/>
+      <c r="S28" s="14" t="inlineStr">
+        <is>
+          <t>$7.93</t>
+        </is>
+      </c>
+      <c r="T28" s="13" t="inlineStr">
+        <is>
+          <t>$11.89</t>
+        </is>
+      </c>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V28" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>Annual performance</t>
+        </is>
+      </c>
+      <c r="X28" s="11" t="inlineStr">
+        <is>
+          <t>$700.00</t>
+        </is>
+      </c>
+      <c r="Y28" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="Z28" s="11" t="inlineStr">
+        <is>
+          <t>$17,200.00</t>
+        </is>
+      </c>
       <c r="AA28" s="11" t="n"/>
-      <c r="AB28" s="11" t="n"/>
-      <c r="AC28" s="11" t="n"/>
-      <c r="AD28" s="11" t="n"/>
-      <c r="AE28" s="11" t="n"/>
-      <c r="AF28" s="11" t="n"/>
-      <c r="AG28" s="11" t="n"/>
+      <c r="AB28" s="11" t="inlineStr">
+        <is>
+          <t>$7.69</t>
+        </is>
+      </c>
+      <c r="AC28" s="11" t="inlineStr">
+        <is>
+          <t>$11.54</t>
+        </is>
+      </c>
+      <c r="AD28" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AE28" s="11" t="inlineStr">
+        <is>
+          <t>$700.00</t>
+        </is>
+      </c>
+      <c r="AF28" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AG28" s="11" t="inlineStr">
+        <is>
+          <t>$16,700.00</t>
+        </is>
+      </c>
       <c r="AH28" s="11" t="n"/>
-      <c r="AI28" s="11" t="n"/>
-      <c r="AJ28" s="11" t="n"/>
-      <c r="AK28" s="11" t="n"/>
-      <c r="AL28" s="11" t="n"/>
-      <c r="AM28" s="11" t="n"/>
-      <c r="AN28" s="11" t="n"/>
+      <c r="AI28" s="11" t="inlineStr">
+        <is>
+          <t>$7.50</t>
+        </is>
+      </c>
+      <c r="AJ28" s="11" t="inlineStr">
+        <is>
+          <t>$11.25</t>
+        </is>
+      </c>
+      <c r="AK28" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AL28" s="11" t="inlineStr">
+        <is>
+          <t>$600.00</t>
+        </is>
+      </c>
+      <c r="AM28" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AN28" s="11" t="inlineStr">
+        <is>
+          <t>$16,200.00</t>
+        </is>
+      </c>
       <c r="AO28" s="11" t="n"/>
-      <c r="AP28" s="11" t="n"/>
-      <c r="AQ28" s="11" t="n"/>
-      <c r="AR28" s="11" t="n"/>
-      <c r="AS28" s="11" t="n"/>
-      <c r="AT28" s="11" t="n"/>
-      <c r="AU28" s="11" t="n"/>
-      <c r="AV28" s="11" t="n"/>
-      <c r="AW28" s="10" t="n"/>
-      <c r="AX28" s="10" t="n"/>
-      <c r="AY28" s="10" t="n"/>
-      <c r="AZ28" s="10" t="n"/>
-      <c r="BA28" s="10" t="n"/>
-      <c r="BB28" s="10" t="n"/>
-      <c r="BC28" s="10" t="n"/>
+      <c r="AP28" s="11" t="inlineStr">
+        <is>
+          <t>$7.26</t>
+        </is>
+      </c>
+      <c r="AQ28" s="11" t="inlineStr">
+        <is>
+          <t>$10.89</t>
+        </is>
+      </c>
+      <c r="AR28" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AS28" s="11" t="inlineStr">
+        <is>
+          <t>$600.00</t>
+        </is>
+      </c>
+      <c r="AT28" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AU28" s="11" t="inlineStr">
+        <is>
+          <t>$15,700.00</t>
+        </is>
+      </c>
+      <c r="AV28" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AW28" s="10" t="inlineStr">
+        <is>
+          <t>EE / Employee Only</t>
+        </is>
+      </c>
+      <c r="AX28" s="10" t="inlineStr">
+        <is>
+          <t>Plan A $2000</t>
+        </is>
+      </c>
+      <c r="AY28" s="10" t="inlineStr">
+        <is>
+          <t>$800.00</t>
+        </is>
+      </c>
+      <c r="AZ28" s="10" t="inlineStr">
+        <is>
+          <t>$720.00</t>
+        </is>
+      </c>
+      <c r="BA28" s="10" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+      <c r="BB28" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC28" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
       <c r="BD28" s="20" t="n"/>
-      <c r="BE28" s="19" t="n"/>
-      <c r="BF28" s="19" t="n"/>
-      <c r="BG28" s="19" t="n"/>
+      <c r="BE28" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BF28" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BG28" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="23" t="n"/>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>ING-E30</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>07/23/1976</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>75751</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Chief Happiness Ninja</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>TX Office</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>04/07/2022</t>
+        </is>
+      </c>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="14" t="n"/>
-      <c r="N29" s="14" t="n"/>
-      <c r="O29" s="14" t="n"/>
-      <c r="P29" s="14" t="n"/>
-      <c r="Q29" s="14" t="n"/>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>Non-Exempt</t>
+        </is>
+      </c>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>Regular Full time (FT)</t>
+        </is>
+      </c>
+      <c r="Q29" s="14" t="inlineStr">
+        <is>
+          <t>Hourly</t>
+        </is>
+      </c>
       <c r="R29" s="14" t="n"/>
-      <c r="S29" s="14" t="n"/>
-      <c r="T29" s="13" t="n"/>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n"/>
-      <c r="W29" s="11" t="n"/>
-      <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="11" t="n"/>
-      <c r="Z29" s="11" t="n"/>
+      <c r="S29" s="14" t="inlineStr">
+        <is>
+          <t>$24.47</t>
+        </is>
+      </c>
+      <c r="T29" s="13" t="inlineStr">
+        <is>
+          <t>$36.70</t>
+        </is>
+      </c>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>Annual performance</t>
+        </is>
+      </c>
+      <c r="X29" s="11" t="inlineStr">
+        <is>
+          <t>$2,100.00</t>
+        </is>
+      </c>
+      <c r="Y29" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="Z29" s="11" t="inlineStr">
+        <is>
+          <t>$53,000.00</t>
+        </is>
+      </c>
       <c r="AA29" s="11" t="n"/>
-      <c r="AB29" s="11" t="n"/>
-      <c r="AC29" s="11" t="n"/>
-      <c r="AD29" s="11" t="n"/>
-      <c r="AE29" s="11" t="n"/>
-      <c r="AF29" s="11" t="n"/>
-      <c r="AG29" s="11" t="n"/>
+      <c r="AB29" s="11" t="inlineStr">
+        <is>
+          <t>$23.75</t>
+        </is>
+      </c>
+      <c r="AC29" s="11" t="inlineStr">
+        <is>
+          <t>$35.62</t>
+        </is>
+      </c>
+      <c r="AD29" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AE29" s="11" t="inlineStr">
+        <is>
+          <t>$2,100.00</t>
+        </is>
+      </c>
+      <c r="AF29" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AG29" s="11" t="inlineStr">
+        <is>
+          <t>$51,500.00</t>
+        </is>
+      </c>
       <c r="AH29" s="11" t="n"/>
-      <c r="AI29" s="11" t="n"/>
-      <c r="AJ29" s="11" t="n"/>
-      <c r="AK29" s="11" t="n"/>
-      <c r="AL29" s="11" t="n"/>
-      <c r="AM29" s="11" t="n"/>
-      <c r="AN29" s="11" t="n"/>
+      <c r="AI29" s="11" t="inlineStr">
+        <is>
+          <t>$23.08</t>
+        </is>
+      </c>
+      <c r="AJ29" s="11" t="inlineStr">
+        <is>
+          <t>$34.62</t>
+        </is>
+      </c>
+      <c r="AK29" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AL29" s="11" t="inlineStr">
+        <is>
+          <t>$2,000.00</t>
+        </is>
+      </c>
+      <c r="AM29" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AN29" s="11" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
       <c r="AO29" s="11" t="n"/>
-      <c r="AP29" s="11" t="n"/>
-      <c r="AQ29" s="11" t="n"/>
-      <c r="AR29" s="11" t="n"/>
-      <c r="AS29" s="11" t="n"/>
-      <c r="AT29" s="11" t="n"/>
-      <c r="AU29" s="11" t="n"/>
-      <c r="AV29" s="11" t="n"/>
-      <c r="AW29" s="10" t="n"/>
-      <c r="AX29" s="10" t="n"/>
-      <c r="AY29" s="10" t="n"/>
-      <c r="AZ29" s="10" t="n"/>
-      <c r="BA29" s="10" t="n"/>
-      <c r="BB29" s="10" t="n"/>
-      <c r="BC29" s="10" t="n"/>
+      <c r="AP29" s="11" t="inlineStr">
+        <is>
+          <t>$22.40</t>
+        </is>
+      </c>
+      <c r="AQ29" s="11" t="inlineStr">
+        <is>
+          <t>$33.60</t>
+        </is>
+      </c>
+      <c r="AR29" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AS29" s="11" t="inlineStr">
+        <is>
+          <t>$1,900.00</t>
+        </is>
+      </c>
+      <c r="AT29" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AU29" s="11" t="inlineStr">
+        <is>
+          <t>$48,500.00</t>
+        </is>
+      </c>
+      <c r="AV29" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AW29" s="10" t="inlineStr">
+        <is>
+          <t>EE / Employee Only</t>
+        </is>
+      </c>
+      <c r="AX29" s="10" t="inlineStr">
+        <is>
+          <t>Plan A $2000</t>
+        </is>
+      </c>
+      <c r="AY29" s="10" t="inlineStr">
+        <is>
+          <t>$800.00</t>
+        </is>
+      </c>
+      <c r="AZ29" s="10" t="inlineStr">
+        <is>
+          <t>$720.00</t>
+        </is>
+      </c>
+      <c r="BA29" s="10" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+      <c r="BB29" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC29" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
       <c r="BD29" s="20" t="n"/>
-      <c r="BE29" s="19" t="n"/>
-      <c r="BF29" s="19" t="n"/>
-      <c r="BG29" s="19" t="n"/>
+      <c r="BE29" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BF29" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BG29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="23" t="n"/>
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>ING-E31</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>04/04/1981</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>75751</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr"/>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>TX Office</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>02/19/2012</t>
+        </is>
+      </c>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
-      <c r="N30" s="14" t="n"/>
-      <c r="O30" s="14" t="n"/>
-      <c r="P30" s="14" t="n"/>
-      <c r="Q30" s="14" t="n"/>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>Non-Exempt</t>
+        </is>
+      </c>
+      <c r="P30" s="14" t="inlineStr">
+        <is>
+          <t>Regular Full time (FT)</t>
+        </is>
+      </c>
+      <c r="Q30" s="14" t="inlineStr">
+        <is>
+          <t>Hourly</t>
+        </is>
+      </c>
       <c r="R30" s="14" t="n"/>
-      <c r="S30" s="14" t="n"/>
-      <c r="T30" s="13" t="n"/>
-      <c r="U30" s="11" t="n"/>
-      <c r="V30" s="11" t="n"/>
-      <c r="W30" s="11" t="n"/>
-      <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="11" t="n"/>
-      <c r="Z30" s="11" t="n"/>
+      <c r="S30" s="14" t="inlineStr">
+        <is>
+          <t>$17.69</t>
+        </is>
+      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t>$26.54</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>Annual performance</t>
+        </is>
+      </c>
+      <c r="X30" s="11" t="inlineStr">
+        <is>
+          <t>$1,500.00</t>
+        </is>
+      </c>
+      <c r="Y30" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="Z30" s="11" t="inlineStr">
+        <is>
+          <t>$38,300.00</t>
+        </is>
+      </c>
       <c r="AA30" s="11" t="n"/>
-      <c r="AB30" s="11" t="n"/>
-      <c r="AC30" s="11" t="n"/>
-      <c r="AD30" s="11" t="n"/>
-      <c r="AE30" s="11" t="n"/>
-      <c r="AF30" s="11" t="n"/>
-      <c r="AG30" s="11" t="n"/>
+      <c r="AB30" s="11" t="inlineStr">
+        <is>
+          <t>$17.16</t>
+        </is>
+      </c>
+      <c r="AC30" s="11" t="inlineStr">
+        <is>
+          <t>$25.74</t>
+        </is>
+      </c>
+      <c r="AD30" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AE30" s="11" t="inlineStr">
+        <is>
+          <t>$1,500.00</t>
+        </is>
+      </c>
+      <c r="AF30" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AG30" s="11" t="inlineStr">
+        <is>
+          <t>$37,200.00</t>
+        </is>
+      </c>
       <c r="AH30" s="11" t="n"/>
-      <c r="AI30" s="11" t="n"/>
-      <c r="AJ30" s="11" t="n"/>
-      <c r="AK30" s="11" t="n"/>
-      <c r="AL30" s="11" t="n"/>
-      <c r="AM30" s="11" t="n"/>
-      <c r="AN30" s="11" t="n"/>
+      <c r="AI30" s="11" t="inlineStr">
+        <is>
+          <t>$16.68</t>
+        </is>
+      </c>
+      <c r="AJ30" s="11" t="inlineStr">
+        <is>
+          <t>$25.02</t>
+        </is>
+      </c>
+      <c r="AK30" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AL30" s="11" t="inlineStr">
+        <is>
+          <t>$1,400.00</t>
+        </is>
+      </c>
+      <c r="AM30" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AN30" s="11" t="inlineStr">
+        <is>
+          <t>$36,100.00</t>
+        </is>
+      </c>
       <c r="AO30" s="11" t="n"/>
-      <c r="AP30" s="11" t="n"/>
-      <c r="AQ30" s="11" t="n"/>
-      <c r="AR30" s="11" t="n"/>
-      <c r="AS30" s="11" t="n"/>
-      <c r="AT30" s="11" t="n"/>
-      <c r="AU30" s="11" t="n"/>
-      <c r="AV30" s="11" t="n"/>
-      <c r="AW30" s="10" t="n"/>
-      <c r="AX30" s="10" t="n"/>
-      <c r="AY30" s="10" t="n"/>
-      <c r="AZ30" s="10" t="n"/>
-      <c r="BA30" s="10" t="n"/>
-      <c r="BB30" s="10" t="n"/>
-      <c r="BC30" s="10" t="n"/>
+      <c r="AP30" s="11" t="inlineStr">
+        <is>
+          <t>$16.15</t>
+        </is>
+      </c>
+      <c r="AQ30" s="11" t="inlineStr">
+        <is>
+          <t>$24.22</t>
+        </is>
+      </c>
+      <c r="AR30" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AS30" s="11" t="inlineStr">
+        <is>
+          <t>$1,400.00</t>
+        </is>
+      </c>
+      <c r="AT30" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AU30" s="11" t="inlineStr">
+        <is>
+          <t>$35,000.00</t>
+        </is>
+      </c>
+      <c r="AV30" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AW30" s="10" t="inlineStr">
+        <is>
+          <t>EE / Employee Only</t>
+        </is>
+      </c>
+      <c r="AX30" s="10" t="inlineStr">
+        <is>
+          <t>Plan A $2000</t>
+        </is>
+      </c>
+      <c r="AY30" s="10" t="inlineStr">
+        <is>
+          <t>$800.00</t>
+        </is>
+      </c>
+      <c r="AZ30" s="10" t="inlineStr">
+        <is>
+          <t>$720.00</t>
+        </is>
+      </c>
+      <c r="BA30" s="10" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+      <c r="BB30" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC30" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
       <c r="BD30" s="20" t="n"/>
-      <c r="BE30" s="19" t="n"/>
-      <c r="BF30" s="19" t="n"/>
-      <c r="BG30" s="19" t="n"/>
+      <c r="BE30" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BF30" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BG30" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="23" t="n"/>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>ING-E32</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>07/27/2000</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>75751</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>11-2022</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Registered Nurses</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>TX Office</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>03/17/2022</t>
+        </is>
+      </c>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="14" t="n"/>
-      <c r="N31" s="14" t="n"/>
-      <c r="O31" s="14" t="n"/>
-      <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="14" t="n"/>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>Non-Exempt</t>
+        </is>
+      </c>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>Regular Full time (FT)</t>
+        </is>
+      </c>
+      <c r="Q31" s="14" t="inlineStr">
+        <is>
+          <t>Hourly</t>
+        </is>
+      </c>
       <c r="R31" s="14" t="n"/>
-      <c r="S31" s="14" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="11" t="n"/>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="11" t="n"/>
-      <c r="Z31" s="11" t="n"/>
+      <c r="S31" s="14" t="inlineStr">
+        <is>
+          <t>$15.82</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t>$23.73</t>
+        </is>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>Annual performance</t>
+        </is>
+      </c>
+      <c r="X31" s="11" t="inlineStr">
+        <is>
+          <t>$1,400.00</t>
+        </is>
+      </c>
+      <c r="Y31" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="Z31" s="11" t="inlineStr">
+        <is>
+          <t>$34,300.00</t>
+        </is>
+      </c>
       <c r="AA31" s="11" t="n"/>
-      <c r="AB31" s="11" t="n"/>
-      <c r="AC31" s="11" t="n"/>
-      <c r="AD31" s="11" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="11" t="n"/>
-      <c r="AG31" s="11" t="n"/>
+      <c r="AB31" s="11" t="inlineStr">
+        <is>
+          <t>$15.38</t>
+        </is>
+      </c>
+      <c r="AC31" s="11" t="inlineStr">
+        <is>
+          <t>$23.07</t>
+        </is>
+      </c>
+      <c r="AD31" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AE31" s="11" t="inlineStr">
+        <is>
+          <t>$1,300.00</t>
+        </is>
+      </c>
+      <c r="AF31" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AG31" s="11" t="inlineStr">
+        <is>
+          <t>$33,300.00</t>
+        </is>
+      </c>
       <c r="AH31" s="11" t="n"/>
-      <c r="AI31" s="11" t="n"/>
-      <c r="AJ31" s="11" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-      <c r="AL31" s="11" t="n"/>
-      <c r="AM31" s="11" t="n"/>
-      <c r="AN31" s="11" t="n"/>
+      <c r="AI31" s="11" t="inlineStr">
+        <is>
+          <t>$14.90</t>
+        </is>
+      </c>
+      <c r="AJ31" s="11" t="inlineStr">
+        <is>
+          <t>$22.35</t>
+        </is>
+      </c>
+      <c r="AK31" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AL31" s="11" t="inlineStr">
+        <is>
+          <t>$1,300.00</t>
+        </is>
+      </c>
+      <c r="AM31" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AN31" s="11" t="inlineStr">
+        <is>
+          <t>$32,300.00</t>
+        </is>
+      </c>
       <c r="AO31" s="11" t="n"/>
-      <c r="AP31" s="11" t="n"/>
-      <c r="AQ31" s="11" t="n"/>
-      <c r="AR31" s="11" t="n"/>
-      <c r="AS31" s="11" t="n"/>
-      <c r="AT31" s="11" t="n"/>
-      <c r="AU31" s="11" t="n"/>
-      <c r="AV31" s="11" t="n"/>
-      <c r="AW31" s="10" t="n"/>
-      <c r="AX31" s="10" t="n"/>
-      <c r="AY31" s="10" t="n"/>
-      <c r="AZ31" s="10" t="n"/>
-      <c r="BA31" s="10" t="n"/>
-      <c r="BB31" s="10" t="n"/>
-      <c r="BC31" s="10" t="n"/>
+      <c r="AP31" s="11" t="inlineStr">
+        <is>
+          <t>$14.47</t>
+        </is>
+      </c>
+      <c r="AQ31" s="11" t="inlineStr">
+        <is>
+          <t>$21.71</t>
+        </is>
+      </c>
+      <c r="AR31" s="11" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="AS31" s="11" t="inlineStr">
+        <is>
+          <t>$1,300.00</t>
+        </is>
+      </c>
+      <c r="AT31" s="11" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="AU31" s="11" t="inlineStr">
+        <is>
+          <t>$31,400.00</t>
+        </is>
+      </c>
+      <c r="AV31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AW31" s="10" t="inlineStr">
+        <is>
+          <t>EE / Employee Only</t>
+        </is>
+      </c>
+      <c r="AX31" s="10" t="inlineStr">
+        <is>
+          <t>Plan A $2000</t>
+        </is>
+      </c>
+      <c r="AY31" s="10" t="inlineStr">
+        <is>
+          <t>$800.00</t>
+        </is>
+      </c>
+      <c r="AZ31" s="10" t="inlineStr">
+        <is>
+          <t>$720.00</t>
+        </is>
+      </c>
+      <c r="BA31" s="10" t="inlineStr">
+        <is>
+          <t>$50.00</t>
+        </is>
+      </c>
+      <c r="BB31" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC31" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
       <c r="BD31" s="20" t="n"/>
-      <c r="BE31" s="19" t="n"/>
-      <c r="BF31" s="19" t="n"/>
-      <c r="BG31" s="19" t="n"/>
+      <c r="BE31" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BF31" s="19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="BG31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="23" t="n"/>
@@ -63566,7 +64382,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-20 19:46 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>

--- a/public/fixtures/edge_ingestion.xlsx
+++ b/public/fixtures/edge_ingestion.xlsx
@@ -53146,7 +53146,7 @@
       </c>
       <c r="B9" s="43" t="inlineStr">
         <is>
-          <t>07/21/2026</t>
+          <t>07/22/2026</t>
         </is>
       </c>
       <c r="C9" s="43" t="n"/>
@@ -53940,12 +53940,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>08/12/1997</t>
+          <t>07/27/1984</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>03/03/2017</t>
+          <t>03/15/2019</t>
         </is>
       </c>
       <c r="L18" s="14" t="n"/>
@@ -54209,7 +54209,7 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>12/04/1985</t>
+          <t>02/10/1971</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -54254,7 +54254,7 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>06/10/2012</t>
+          <t>08/02/2024</t>
         </is>
       </c>
       <c r="L19" s="14" t="n"/>
@@ -54804,7 +54804,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>11/19/1984</t>
+          <t>07/23/1988</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>09/04/2017</t>
+          <t>01/08/2020</t>
         </is>
       </c>
       <c r="L22" s="14" t="n"/>
@@ -55073,7 +55073,7 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>11/19/1984</t>
+          <t>07/23/1988</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -55118,7 +55118,7 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>09/04/2017</t>
+          <t>01/08/2020</t>
         </is>
       </c>
       <c r="L23" s="14" t="n"/>
@@ -55342,12 +55342,12 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>12/04/1989</t>
+          <t>07/03/1976</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -55387,7 +55387,7 @@
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>06/16/2017</t>
+          <t>12/23/2022</t>
         </is>
       </c>
       <c r="L24" s="14" t="n"/>
@@ -55611,12 +55611,12 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>04/24/1997</t>
+          <t>11/19/1964</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -55656,7 +55656,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>03/17/2016</t>
+          <t>06/08/2013</t>
         </is>
       </c>
       <c r="L25" s="14" t="n"/>
@@ -55876,7 +55876,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>11/23/1984</t>
+          <t>05/25/1970</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -55921,7 +55921,7 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>03/11/2014</t>
+          <t>04/17/2015</t>
         </is>
       </c>
       <c r="L26" s="14" t="n"/>
@@ -56141,12 +56141,12 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>04/04/1985</t>
+          <t>07/19/1992</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -56182,7 +56182,7 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>08/10/2016</t>
+          <t>07/01/2021</t>
         </is>
       </c>
       <c r="L27" s="14" t="n"/>
@@ -56406,12 +56406,12 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>11/19/1968</t>
+          <t>08/16/1997</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>06/11/2014</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="L28" s="14" t="n"/>
@@ -56667,12 +56667,12 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>07/23/1976</t>
+          <t>10/18/1987</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -56708,7 +56708,7 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>04/07/2022</t>
+          <t>08/06/2018</t>
         </is>
       </c>
       <c r="L29" s="14" t="n"/>
@@ -56932,7 +56932,7 @@
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>04/04/1981</t>
+          <t>04/20/1989</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -56973,7 +56973,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>02/19/2012</t>
+          <t>03/06/2020</t>
         </is>
       </c>
       <c r="L30" s="14" t="n"/>
@@ -57197,12 +57197,12 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>07/27/2000</t>
+          <t>12/16/1977</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -57242,7 +57242,7 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>03/17/2022</t>
+          <t>08/24/2019</t>
         </is>
       </c>
       <c r="L31" s="14" t="n"/>
@@ -64382,7 +64382,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-07-21 18:04 from the reference warehouse (public.ext_*)</t>
+          <t>generated 2026-07-22 14:38 from the reference warehouse (public.ext_*)</t>
         </is>
       </c>
     </row>
